--- a/extenbooks/S606.xlsx
+++ b/extenbooks/S606.xlsx
@@ -904,7 +904,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>calculated</t>
+          <t>book_period_validated</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S606.xlsx
+++ b/extenbooks/S606.xlsx
@@ -793,7 +793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B60"/>
+  <dimension ref="A1:B62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -892,7 +892,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1952–2024</t>
+          <t>1952-1989</t>
         </is>
       </c>
     </row>
@@ -954,54 +954,55 @@
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Subseries</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>source / role</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>S606-A</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>S&amp;T 1994</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>DPR (markdown)</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t># S606 — Government Services Workers (G_w)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>**Chapter**: 6 — The Net Social Wage</t>
-        </is>
-      </c>
+      <c r="B18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>**Source Table**: Appendix Ch6 — `Table6_2_BenefitAccounts.csv`, column `govt_services_workers`</t>
+          <t># S606 — Government Services Workers (G_w)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>**Units**: billions_usd</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>**Period**: 1952–1989 (book; S607 extends through 2024 via Table6_3_Extended)</t>
+          <t>**Chapter**: 6 — The Net Social Wage</t>
         </is>
       </c>
     </row>
@@ -1009,7 +1010,7 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>**Content Type**: time_series</t>
+          <t>**Source Table**: Appendix Ch6 — `Table6_2_BenefitAccounts.csv`, column `govt_services_workers`</t>
         </is>
       </c>
     </row>
@@ -1017,31 +1018,39 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>**Status**: calculated</t>
+          <t>**Units**: billions_usd</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>**Period**: 1952–1989 (book; S607 extends through 2024 via Table6_3_Extended)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>## Definition</t>
+          <t>**Content Type**: time_series</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>**Status**: book_period_validated</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Imputed value of free government services consumed by workers (education, public health, etc.) following Tonak's methodology.</t>
+          <t>## Definition</t>
         </is>
       </c>
     </row>
@@ -1053,7 +1062,7 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>## Source</t>
+          <t>Imputed value of free government services consumed by workers (education, public health, etc.) following Tonak's methodology.</t>
         </is>
       </c>
     </row>
@@ -1065,7 +1074,7 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>`data/source/book_tables/Table6_2_BenefitAccounts.csv` (digitized from book Appendix 6 tables). Loader applies a millions→billions conversion when needed; the DPR's "Reference Values" line below shows the converted (billions) figures.</t>
+          <t>## Source</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1086,7 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>## Construction</t>
+          <t>`data/source/book_tables/Table6_2_BenefitAccounts.csv` (digitized from book Appendix 6 tables). Loader applies a millions→billions conversion when needed; the DPR's "Reference Values" line below shows the converted (billions) figures.</t>
         </is>
       </c>
     </row>
@@ -1089,7 +1098,7 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Pass-through loader: read column from the digitized book table, divide by 1000 to convert MILLIONS→BILLIONS for unit consistency with the registry's `units: billions_usd` field, write to intermediate + final stages.</t>
+          <t>## Construction</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1110,7 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>## Reference Values (Validation Benchmarks)</t>
+          <t>Pass-through loader: read column from the digitized book table, divide by 1000 to convert MILLIONS→BILLIONS for unit consistency with the registry's `units: billions_usd` field, write to intermediate + final stages.</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1122,7 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1952=32.69B; 1989=494.80B</t>
+          <t>## Reference Values (Validation Benchmarks)</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1134,7 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Tolerance class: `dollar_series`. Validator script: `code/V03_validators/V03_S606_govt_services_workers.py`. Both endpoints PASS.</t>
+          <t>1952=32.69B; 1989=494.80B</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1146,7 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>## Provenance Chain</t>
+          <t>Tolerance class: `dollar_series`. Validator script: `code/V03_validators/V03_S606_govt_services_workers.py`. Both endpoints PASS.</t>
         </is>
       </c>
     </row>
@@ -1149,23 +1158,19 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>```</t>
+          <t>## Provenance Chain</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>data/source/book_tables/Table6_2_BenefitAccounts.csv</t>
-        </is>
-      </c>
+      <c r="B46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve">  └── code/L01_loaders/L01_S606_govt_services_workers.py</t>
+          <t>```</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1178,7 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">       └── data/intermediate/S606.csv</t>
+          <t>data/source/book_tables/Table6_2_BenefitAccounts.csv</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1186,7 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">            └── code/P02_processors/P02_S606_govt_services_workers.py</t>
+          <t xml:space="preserve">  └── code/L01_loaders/L01_S606_govt_services_workers.py</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1194,7 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">                 └── data/final/S606.csv</t>
+          <t xml:space="preserve">       └── data/intermediate/S606.csv</t>
         </is>
       </c>
     </row>
@@ -1197,7 +1202,7 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">                      └── code/V03_validators/V03_S606_govt_services_workers.py</t>
+          <t xml:space="preserve">            └── code/P02_processors/P02_S606_govt_services_workers.py</t>
         </is>
       </c>
     </row>
@@ -1205,19 +1210,23 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>```</t>
+          <t xml:space="preserve">                 └── data/final/S606.csv</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
-      <c r="B53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                      └── code/V03_validators/V03_S606_govt_services_workers.py</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>## Citation</t>
+          <t>```</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1238,7 @@
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press. Chapter 6 — The Net Social Wage. Appendix tables in Tonak's PhD work (1984) and updated NIPA-based reconstructions through 1989.</t>
+          <t>## Citation</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1250,7 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press. Chapter 6 — The Net Social Wage. Appendix tables in Tonak's PhD work (1984) and updated NIPA-based reconstructions through 1989.</t>
         </is>
       </c>
     </row>
@@ -1252,6 +1261,18 @@
     <row r="60">
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr"/>
+      <c r="B61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
         <is>
           <t>*Generated by anu-ingestion (re-authored from scratch against the Anu Framework v10.0 standard).*</t>
         </is>
@@ -1268,12 +1289,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1296,179 +1317,278 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>methodology_description</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>G_w captures government expenditures on services that benefit workers: public education, public health services, transportation infrastructure, and other general government services × worker share. Worker share is estimated by usage patterns: education allocated by enrollment demographics, health by income-based utilization, infrastructure by commuter/residential usage.</t>
+          <t>Group II - Social consumption (workers' share = labor income/personal income): Education; Health and hospitals; Recreational and cultural activities; Energy; Natural resources; Transportation (adjusted by gas share of passenger cars); Postal services.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ST_1994, Ch6; CHAPTER_6_INVESTIGATION.md</t>
+          <t>ST_1994, Appendix N (Expenditure Classification, Group II); KB chunk_38 lines 226-233</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>data_source</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Government consumption expenditures from NIPA Table 3.1 (Government Current Expenditures). Education spending from federal (Table 3.2) and state/local (Table 3.3) sources. Health expenditure from CMS National Health Expenditure data. Infrastructure spending from NIPA government investment tables.</t>
+          <t>Group III - Excluded from labor consumption: (a) Faux frais of capitalist society (Marx 1977, p. 446): Central executive, legislative, judicial activities; International affairs; Space; National defense; Civilian safety; Veteran benefits; Agriculture.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BEA NIPA Tables 3.1, 3.2, 3.3; CMS NHE data</t>
+          <t>ST_1994, Appendix N (Expenditure Classification, Group III(a)); KB chunk_38 lines 235-243</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>methodological_note</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Government services allocation is the most assumption-sensitive component of the NSW framework. Military spending is excluded from worker services (it protects capital and labor equally, but benefits primarily accrue to capital through protection of property rights and foreign investment). Police and judicial services are similarly excluded or given minimal worker allocation.</t>
+          <t>Group II (labor share = 0.727) 1964: Education 27.6 -&gt; 20.1; Health and hospitals 6.4 -&gt; 4.7; Recreational and cultural activities 1.2 -&gt; 0.9; Energy 1.0 -&gt; 0.7; Natural resources 2.0 -&gt; 1.5; Postal service 0.8 -&gt; 0.6; Transportation 13.1 -&gt; 6.7 (+ gas adjustment).</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ST_1994, Ch6</t>
+          <t>ST_1994, Table N.1 Group II expenditures 1964; KB chunk_38 lines 285-292</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>empirical_finding</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Public education is the largest component of G_w, reflecting both K-12 and public higher education spending. Education spending growth was driven by enrollment expansion (baby boom cohorts), teacher salary increases, and state/local revenue growth. Health services grew significantly after 1966 with the expansion of public health programs.</t>
+          <t>Transportation adjusted by gas share of passenger cars (Tonak 1984, chap. IV, apx. II).</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CHAPTER_6_INVESTIGATION.md</t>
+          <t>ST_1994, Appendix N methodology notes; KB chunk_38 line 324</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>cross_study_comparison</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Moos and Tonak differ on the scope of government services included. Tonak uses a narrower definition focused on direct consumption services; Moos includes some infrastructure spending. The AS2 extension follows Tonak's narrower scope for the historical period and Moos's broader scope for the extension period, with a reconciliation adjustment.</t>
+          <t>(b) Capitalist-directed expenditures: Economic development, regulation, services; Net interest (to highest income brackets); Others and unallocables (small businesses, related administration).</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NSW_COMPARISON_REVIEW.md</t>
+          <t>ST_1994, Appendix N (Expenditure Classification, Group III(b)); KB chunk_38 lines 244-247</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>decision_log_note</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DEC-006 (2026-03-30): The 1996 welfare reform changed the composition of government services available to workers, particularly in means-tested program structures. NIPA Table 3.1 continuous coverage bridges this transition. S606 shows a structural break around 1996-1997 — documented in V03 continuity checks but not adjusted. Note: Per DEC-013, government consumption (E2: education, health, transportation from NIPA T3.16) is retained in L17 but excluded from the Moos NSW formula — included here in G_w under the broader Shaikh-Tonak definition.</t>
+          <t>Property taxes: Only homeowner portion, then x labor share (Tonak 1984, chap. IV, apx. I).</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NickyData/DECISION_LOG.md, DEC-006; DEC-013</t>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
+          <t>ST_1994, Appendix N methodology notes; KB chunk_38 line 325</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>verbatim_quote</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Labor share 1964: 0.727 (labor income / personal income).</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ST_1994, Table N.1 data sources; KB chunk_38 line 321</t>
+        </is>
+      </c>
+    </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>methodology_summary</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Government services to workers allocate public education, health, and infrastructure spending by worker usage share. Military and police spending excluded. Education is the dominant component. DEC-006: 1996 welfare reform structural break handled via NIPA continuous coverage; break documented in V03.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
+          <t>Exception: Military disability and military retirement (treated as costs of war, excluded).</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ST_1994, Appendix N (Group I exclusion); KB chunk_38 line 224</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>verbatim_quote</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>For Phase 1 NSW: Government as secondary sector receiving transfers from primary; Cannot double-count government revenues; Must track actual uses of product induced by government expenditures.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ST_1994, Ch7 Section 7.2 application to NSW; KB chunk_24 lines 410-413</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>known_issues:</t>
+          <t>methodology_description</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>G_w captures government expenditures on services that benefit workers: public education, public health services, transportation infrastructure, and other general government services × worker share. Worker share is estimated by usage patterns: education allocated by enrollment demographics, health by income-based utilization, infrastructure by commuter/residential usage.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ST_1994, Ch6; CHAPTER_6_INVESTIGATION.md</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>data_source</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Military/police exclusion is theoretically motivated but empirically debatable</t>
+          <t>Government consumption expenditures from NIPA Table 3.1 (Government Current Expenditures). Education spending from federal (Table 3.2) and state/local (Table 3.3) sources. Health expenditure from CMS National Health Expenditure data. Infrastructure spending from NIPA government investment tables.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>BEA NIPA Tables 3.1, 3.2, 3.3; CMS NHE data</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>methodological_note</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Worker share of education spending changes with demographic shifts</t>
+          <t>Government services allocation is the most assumption-sensitive component of the NSW framework. Military spending is excluded from worker services (it protects capital and labor equally, but benefits primarily accrue to capital through protection of property rights and foreign investment). Police and judicial services are similarly excluded or given minimal worker allocation.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ST_1994, Ch6</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>empirical_finding</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Infrastructure allocation between workers and capital is highly approximate</t>
+          <t>Public education is the largest component of G_w, reflecting both K-12 and public higher education spending. Education spending growth was driven by enrollment expansion (baby boom cohorts), teacher salary increases, and state/local revenue growth. Health services grew significantly after 1966 with the expansion of public health programs.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CHAPTER_6_INVESTIGATION.md</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>cross_study_comparison</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Scope difference between Tonak (narrow) and Moos (broad) definitions creates reconciliation challenges</t>
+          <t>Moos and Tonak differ on the scope of government services included. Tonak uses a narrower definition focused on direct consumption services; Moos includes some infrastructure spending. The AS2 extension follows Tonak's narrower scope for the historical period and Moos's broader scope for the extension period, with a reconciliation adjustment.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NSW_COMPARISON_REVIEW.md</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>decision_log_note</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1996 welfare reform structural break documented in V03 continuity checks (DEC-006)</t>
+          <t>[internal-decision-record] (2026-03-30): The 1996 welfare reform changed the composition of government services available to workers, particularly in means-tested program structures. NIPA Table 3.1 continuous coverage bridges this transition. S606 shows a structural break around 1996-1997 — documented in V03 continuity checks but not adjusted. Note: Per [internal-decision-record], government consumption (E2: education, health, transportation from NIPA T3.16) is retained in L17 but excluded from the Moos NSW formula — included here in G_w under the broader Shaikh-Tonak definition.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[internal-decision-log], [internal-decision-record]; [internal-decision-record]</t>
         </is>
       </c>
     </row>
     <row r="17"/>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>cross_references:</t>
-        </is>
-      </c>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>VERBATIM QUOTES (top-level)</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr"/>
+      <c r="C18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>S604</t>
+          <t>Group II - Social consumption (workers' share = labor income/personal income): Education; Health and hospitals; Recreational and cultural activities; Energy; Natural resources; Transportation (adjusted by gas share of passenger cars); Postal services.</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ST_1994, Appendix N (Expenditure Classification, Group II); KB chunk_38 lines 226-233</t>
         </is>
       </c>
     </row>
@@ -1476,7 +1596,12 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>S605</t>
+          <t>Group III - Excluded from labor consumption: (a) Faux frais of capitalist society (Marx 1977, p. 446): Central executive, legislative, judicial activities; International affairs; Space; National defense; Civilian safety; Veteran benefits; Agriculture.</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ST_1994, Appendix N (Expenditure Classification, Group III(a)); KB chunk_38 lines 235-243</t>
         </is>
       </c>
     </row>
@@ -1484,49 +1609,225 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
+          <t>Group II (labor share = 0.727) 1964: Education 27.6 -&gt; 20.1; Health and hospitals 6.4 -&gt; 4.7; Recreational and cultural activities 1.2 -&gt; 0.9; Energy 1.0 -&gt; 0.7; Natural resources 2.0 -&gt; 1.5; Postal service 0.8 -&gt; 0.6; Transportation 13.1 -&gt; 6.7 (+ gas adjustment).</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ST_1994, Table N.1 Group II expenditures 1964; KB chunk_38 lines 285-292</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Transportation adjusted by gas share of passenger cars (Tonak 1984, chap. IV, apx. II).</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ST_1994, Appendix N methodology notes; KB chunk_38 line 324</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>(b) Capitalist-directed expenditures: Economic development, regulation, services; Net interest (to highest income brackets); Others and unallocables (small businesses, related administration).</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ST_1994, Appendix N (Expenditure Classification, Group III(b)); KB chunk_38 lines 244-247</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Property taxes: Only homeowner portion, then x labor share (Tonak 1984, chap. IV, apx. I).</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ST_1994, Appendix N methodology notes; KB chunk_38 line 325</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Labor share 1964: 0.727 (labor income / personal income).</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ST_1994, Table N.1 data sources; KB chunk_38 line 321</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Exception: Military disability and military retirement (treated as costs of war, excluded).</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ST_1994, Appendix N (Group I exclusion); KB chunk_38 line 224</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>For Phase 1 NSW: Government as secondary sector receiving transfers from primary; Cannot double-count government revenues; Must track actual uses of product induced by government expenditures.</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ST_1994, Ch7 Section 7.2 application to NSW; KB chunk_24 lines 410-413</t>
+        </is>
+      </c>
+    </row>
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>methodology_summary</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Government services to workers allocate public education, health, and infrastructure spending by worker usage share. Military and police spending excluded. Education is the dominant component. [internal-decision-record]: 1996 welfare reform structural break handled via NIPA continuous coverage; break documented in V03.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>known_issues:</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Military/police exclusion is theoretically motivated but empirically debatable</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Worker share of education spending changes with demographic shifts</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Infrastructure allocation between workers and capital is highly approximate</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Scope difference between Tonak (narrow) and Moos (broad) definitions creates reconciliation challenges</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>1996 welfare reform structural break documented in V03 continuity checks ([internal-decision-record])</t>
+        </is>
+      </c>
+    </row>
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>cross_references:</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>S604</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>S605</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
           <t>S607</t>
         </is>
       </c>
     </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="42"/>
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>citations:</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>ST_1994</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>BEA_NIPA</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>Bureau of Economic Analysis. National Income and Product Accounts. https://apps.bea.gov/iTable/</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>Moos_2017</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>Moos, Julie. 2017. The Net Social Wage in the United States, 1952-2012. PhD dissertation.</t>
         </is>
@@ -1543,7 +1844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1606,7 +1907,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>null — series does not extend beyond book period</t>
+          <t>null - series does not extend beyond book period</t>
         </is>
       </c>
     </row>
@@ -1627,7 +1928,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"1952": 32.6949, "1989": 494.8035}</t>
         </is>
       </c>
     </row>
@@ -1651,7 +1952,43 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>level_series</t>
+          <t>dollar_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>tolerance_class</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dollar_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>tolerance_rel</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>tolerance_abs</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1.0</t>
         </is>
       </c>
     </row>
